--- a/experiments/results/resnet34/CIFAR-10/ReAct+DICE/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/ReAct+DICE/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -960,6 +960,202 @@
       <c r="O12" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=1.0,scale_th=1.0,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>96.34999999999999</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>96.69</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.1,scale_th=1.0,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.1,scale_th=1.1,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>95.66</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>94.17</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>26.34</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.1,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>96.79000000000001</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>25.63</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=1.1,scale_th=1.1,type=avg</t>
         </is>
       </c>
     </row>
